--- a/Tables/STAGE_COMP_DATA.xlsx
+++ b/Tables/STAGE_COMP_DATA.xlsx
@@ -966,32 +966,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Label</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">EnemyKey</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필드</t>
+          <t xml:space="preserve">한글 라벨</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한글 라벨</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">수치</t>
         </is>
@@ -1000,60 +985,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t xml:space="preserve">보병</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t xml:space="preserve">포격</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t xml:space="preserve">장갑</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="B5">
         <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t xml:space="preserve">강적</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="B6">
         <v>4</v>
       </c>
     </row>
@@ -1067,133 +1032,69 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">STAGE_COMP_DATA 테이블 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">INDEX</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FieldName</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DataType</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번호</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">필드명</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">간략 설명</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 타입</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 예시</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">필드 설명/값</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고(근거)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dev_Index</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발용 번호</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
+          <t xml:space="preserve">필드 설명 / 값</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dev_Desc</t>
+          <t xml:space="preserve">Dev_Index</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">개발용 설명</t>
+          <t xml:space="preserve">개발용 번호</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S1 infantry</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1202,156 +1103,158 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지와 적을 한눈에</t>
+          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Dev_Desc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유 번호</t>
+          <t xml:space="preserve">개발용 설명</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>1</v>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 infantry</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1부터</t>
+          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">행 식별</t>
+          <t xml:space="preserve">스테이지와 적을 한눈에</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">StageID</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지</t>
+          <t xml:space="preserve">고유 번호</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S1</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1~S6</t>
+          <t xml:space="preserve">1부터</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance_v4.json stages[].id</t>
+          <t xml:space="preserve">행 식별</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
+          <t xml:space="preserve">StageID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">적 종류</t>
+          <t xml:space="preserve">스테이지</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">enum</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>1</v>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">보병1 포격2 장갑3 강적4</t>
+          <t xml:space="preserve">S1~S6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Designer_Data 참조</t>
+          <t xml:space="preserve">balance_v4.json stages[].id</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count</t>
+          <t xml:space="preserve">EnemyKey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">마리 수</t>
+          <t xml:space="preserve">적 종류</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">enum</t>
         </is>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 스테이지에 나오는 수</t>
+          <t xml:space="preserve">보병1 포격2 장갑3 강적4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">json composition[].count</t>
+          <t xml:space="preserve">Designer_Data 참조</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hp</t>
+          <t xml:space="preserve">Count</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">체력</t>
+          <t xml:space="preserve">마리 수</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1360,31 +1263,31 @@
         </is>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 마리 체력</t>
+          <t xml:space="preserve">그 스테이지에 나오는 수</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">json composition[].hp · §72-14 가정값 · **HP 상승폭 절반 09-18 사용자 확정** · S5·S6 불변</t>
+          <t xml:space="preserve">json composition[].count</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Def</t>
+          <t xml:space="preserve">Hp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">방어</t>
+          <t xml:space="preserve">체력</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1393,47 +1296,80 @@
         </is>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 마리 방어</t>
+          <t xml:space="preserve">한 마리 체력</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">json composition[].def · 09-18 에 안 바뀌었다</t>
+          <t xml:space="preserve">json composition[].hp · §72-14 가정값 · **HP 상승폭 절반 09-18 사용자 확정** · S5·S6 불변</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Def</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방어</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 마리 방어</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json composition[].def · 09-18 에 안 바뀌었다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">bool</t>
         </is>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">1=확정 0=가정</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">json stages[].compConfirmed 그대로 — **S1~S4 는 0 · S5·S6 은 1**</t>
         </is>
